--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v2/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v2/EVAL_SUMMARY.xlsx
@@ -541,13 +541,13 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="O2" t="n">
         <v>0.364</v>
@@ -600,13 +600,13 @@
         <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="O3" t="n">
         <v>0.364</v>
@@ -659,13 +659,13 @@
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="O4" t="n">
         <v>0.364</v>
@@ -784,13 +784,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="I2" t="n">
         <v>0.364</v>
